--- a/dane.xlsx
+++ b/dane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Projekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pobrane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961209E7-7E66-449E-82ED-C4809E73B905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C22408-5C63-4242-A42C-7B7A40A40108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4356" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{CCE6293E-D9DC-4876-959E-95B92FF9D560}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCE6293E-D9DC-4876-959E-95B92FF9D560}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Kod</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>Okapi</t>
+  </si>
+  <si>
+    <t>chyba się zapadło</t>
+  </si>
+  <si>
+    <t>Dettel</t>
   </si>
 </sst>
 </file>
@@ -442,13 +448,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0201011-7036-4510-9547-ADE0141B700E}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,7 +474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>12345</v>
       </c>
@@ -488,7 +494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>23456</v>
       </c>
@@ -506,6 +512,26 @@
       </c>
       <c r="F3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>45678</v>
+      </c>
+      <c r="B4">
+        <v>34522</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46039</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -514,6 +540,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008C36B55BE93FA8448AF54114A5AA3429" ma:contentTypeVersion="0" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="42d7fc06fbf51657a5f3ba03fed0f9fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b58407e99af425f499b730f67c7bf4f7">
     <xsd:element name="properties">
@@ -627,15 +662,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -643,13 +669,34 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD21B08-32F3-4A71-AAB1-75F52E367C82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B4D654-9E80-4865-98CC-D187D6920E23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B4D654-9E80-4865-98CC-D187D6920E23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD21B08-32F3-4A71-AAB1-75F52E367C82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF771D7-3813-4994-BE3F-EB2A9F6A0DDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF771D7-3813-4994-BE3F-EB2A9F6A0DDD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dane.xlsx
+++ b/dane.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pobrane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C22408-5C63-4242-A42C-7B7A40A40108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D962F1-3BA1-42E5-81AA-A34394BE7DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCE6293E-D9DC-4876-959E-95B92FF9D560}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>Kod</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Dettel</t>
+  </si>
+  <si>
+    <t>dla testów</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0201011-7036-4510-9547-ADE0141B700E}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
@@ -534,21 +537,32 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>32134</v>
+      </c>
+      <c r="B5">
+        <v>44444</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46064</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008C36B55BE93FA8448AF54114A5AA3429" ma:contentTypeVersion="0" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="42d7fc06fbf51657a5f3ba03fed0f9fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b58407e99af425f499b730f67c7bf4f7">
     <xsd:element name="properties">
@@ -662,6 +676,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -669,14 +692,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B4D654-9E80-4865-98CC-D187D6920E23}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD21B08-32F3-4A71-AAB1-75F52E367C82}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -692,6 +707,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B4D654-9E80-4865-98CC-D187D6920E23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF771D7-3813-4994-BE3F-EB2A9F6A0DDD}">
   <ds:schemaRefs>
